--- a/invoice_data.xlsx
+++ b/invoice_data.xlsx
@@ -425,12 +425,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="67" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -494,6 +494,72 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>template2bill company
+32311 address
+template2 321311</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>template2ship company
+99991 address
+template2 44444</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>09/06/2022</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2,343.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>4955 Tecumsah Lane
+Shongaloo, Louisiana(L
+71072
+318-846-2191</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>6678411</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4955 Tecumsah Lane
+, Shongaloo,
+Louisiana(LA), 71072
+318-846-2191</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20/10/2021</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>99,056.43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
